--- a/artfynd/A 51488-2024 artfynd.xlsx
+++ b/artfynd/A 51488-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121614067</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51488-2024 artfynd.xlsx
+++ b/artfynd/A 51488-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121614067</v>
       </c>
       <c r="B2" t="n">
-        <v>57508</v>
+        <v>57516</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51488-2024 artfynd.xlsx
+++ b/artfynd/A 51488-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121614067</v>
+        <v>92877190</v>
       </c>
       <c r="B2" t="n">
-        <v>57516</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 51488, Loftern, Sm</t>
+          <t>Loftern, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563504</v>
+        <v>564030</v>
       </c>
       <c r="R2" t="n">
-        <v>6434513</v>
+        <v>6434280</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,21 +757,675 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121614067</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 51488, Loftern, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>563504</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6434513</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>92877704</v>
+      </c>
+      <c r="B4" t="n">
+        <v>84149</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>204936</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Praktscharlakansskål</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcoscypha coccinea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Jacq.:Fr.) Lambotte</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Loftern, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>563945</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6434398</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-04-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-04-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96208809</v>
+      </c>
+      <c r="B5" t="n">
+        <v>111176</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Loftern, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>563654</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6434459</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer på en grov asp samt på minst fyra ytterligare träd i närheten,</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Kent Gullquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121614037</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111176</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Loftern, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>563656</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6434457</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt på bl a 3 träd</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121614049</v>
+      </c>
+      <c r="B7" t="n">
+        <v>111176</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 51488, Loftern, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>563590</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6434469</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt på ngt träd + på marken</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>92877531</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Loftern, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>563945</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6434398</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-04-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-04-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
